--- a/InputData/web-app/BpTPEU/BTU per Total Primary Energy Unit.xlsx
+++ b/InputData/web-app/BpTPEU/BTU per Total Primary Energy Unit.xlsx
@@ -5,35 +5,23 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Documents\eps-hongkong\InputData\web-app\BpTPEU\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeRepositories\eps-us\InputData\web-app\BpTPEU\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="720" yWindow="390" windowWidth="27555" windowHeight="14100"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="BpTPEU" sheetId="2" r:id="rId2"/>
+    <sheet name="BpTPEU-large" sheetId="2" r:id="rId2"/>
+    <sheet name="BpTPEU-small" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
-  <si>
-    <t>BpTPEU BTU per Total Primary Energy Unit</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>Source:</t>
   </si>
@@ -47,19 +35,25 @@
     <t>none needed</t>
   </si>
   <si>
-    <t>=</t>
-  </si>
-  <si>
-    <t>For Hong Kong, the unit for Total Primary Energy output is TJ.</t>
-  </si>
-  <si>
-    <t>TJ</t>
-  </si>
-  <si>
-    <t>J</t>
-  </si>
-  <si>
-    <t>One TJ</t>
+    <t>For the U.S.:</t>
+  </si>
+  <si>
+    <t>large primary energy output unit</t>
+  </si>
+  <si>
+    <t>small primary energy output unit</t>
+  </si>
+  <si>
+    <t>The large primary energy output unit (used in totals graphs) is: quadrillion BTU</t>
+  </si>
+  <si>
+    <t>The small primary energy output unit (used in energy intensity per unit GDP graphs) is: thousand BTU</t>
+  </si>
+  <si>
+    <t>BpTPEU BTU per Large Primary Energy Unit</t>
+  </si>
+  <si>
+    <t>BpTPEU BTU per Small Primary Energy Unit</t>
   </si>
 </sst>
 </file>
@@ -110,9 +104,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -417,78 +409,53 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A3" s="1" t="s">
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="2"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="B4" s="2"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A8" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A11">
-        <v>1</v>
-      </c>
-      <c r="B11" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11">
-        <v>1055</v>
-      </c>
-      <c r="E11" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A12">
-        <v>1</v>
-      </c>
-      <c r="B12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="3">
-        <f>A11/D11*10^12</f>
-        <v>947867298.57819903</v>
-      </c>
-      <c r="E12" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="D15" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -498,29 +465,29 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B1" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" s="3">
-        <f>About!D12</f>
-        <v>947867298.57819903</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+        <f>10^15</f>
+        <v>1000000000000000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B9" s="3"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" s="3"/>
     </row>
   </sheetData>
@@ -528,11 +495,47 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="3"/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="4">
+        <f>10^3</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B9" s="3"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B10" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010005D5DE895D8AE54A972C2171818FD093" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f85f6924c4aafd897c3f23384ae9dc35">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="01f24951-2a3e-4fd5-a813-71a74687f653" xmlns:ns3="80a27e12-bb1f-4e28-b766-51f62aa5c67e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="11afb4ea5aef950dd888cd3ab39ccec1" ns2:_="" ns3:_="">
-    <xsd:import namespace="01f24951-2a3e-4fd5-a813-71a74687f653"/>
-    <xsd:import namespace="80a27e12-bb1f-4e28-b766-51f62aa5c67e"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D257B2780BAD0A45A02FA065B9C6CC6A" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="54b727ac31dab95898e9cf92f0402afe">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" xmlns:ns3="6b15a3a4-8173-42d6-9deb-398ec38eca4b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="42611c3eb46fef4c2b2610d1e51cc1b0" ns2:_="" ns3:_="">
+    <xsd:import namespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433"/>
+    <xsd:import namespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -541,16 +544,20 @@
               <xsd:all>
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -558,7 +565,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="01f24951-2a3e-4fd5-a813-71a74687f653" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -571,55 +578,72 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="12" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="13" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="13" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="14" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="15" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="18" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="19" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ca0deac2-43b9-460d-a4eb-012f87ec990e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="80a27e12-bb1f-4e28-b766-51f62aa5c67e" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="16" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -638,12 +662,23 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="17" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{caf201a3-c970-477d-b8ee-c5923cb026e5}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="6b15a3a4-8173-42d6-9deb-398ec38eca4b">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -754,44 +789,10 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D2D73D3-462E-4CC3-993B-219026AE3A63}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="01f24951-2a3e-4fd5-a813-71a74687f653"/>
-    <ds:schemaRef ds:uri="80a27e12-bb1f-4e28-b766-51f62aa5c67e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CE3BDA9-D76A-47C9-B282-17AA98E9EE43}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{651AFD69-AA5F-4614-AEC0-A0DAE2B6030C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B67C0D24-F5B6-480D-A2EF-F01CFA1BA16A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3880B69A-E88F-4EBB-9957-2B1D08383C5D}"/>
 </file>